--- a/france_stress_test/output/tables/france_stress_summary.xlsx
+++ b/france_stress_test/output/tables/france_stress_summary.xlsx
@@ -531,19 +531,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>0.7016131249999999</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0.54278125</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0.8508065625</v>
       </c>
       <c r="G2" t="n">
-        <v>4.300924565274036</v>
+        <v>4.096139971524036</v>
       </c>
       <c r="H2" t="n">
         <v>299.8683249657738</v>
@@ -564,20 +564,20 @@
         <v>0.03765520392754559</v>
       </c>
       <c r="N2" t="n">
-        <v>1984713.336006569</v>
+        <v>1622274.833043017</v>
       </c>
       <c r="O2" t="n">
-        <v>0.5328125</v>
+        <v>0.6676360501534597</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9933071490757153</v>
+        <v>0.8169483812668784</v>
       </c>
       <c r="Q2" t="n">
-        <v>10.45674274767531</v>
+        <v>10.49790379697857</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>CONDITIONAL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -603,19 +603,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.83</v>
+        <v>0.5485183333333333</v>
       </c>
       <c r="D3" t="n">
         <v>0.8</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8</v>
+        <v>0.4519166666666667</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.6742591666666666</v>
       </c>
       <c r="G3" t="n">
-        <v>4.093027649453166</v>
+        <v>3.933476232786501</v>
       </c>
       <c r="H3" t="n">
         <v>377.9349180103374</v>
@@ -636,20 +636,20 @@
         <v>0.04417940159529692</v>
       </c>
       <c r="N3" t="n">
-        <v>1523220.433837877</v>
+        <v>912987.2321469961</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2640000000000001</v>
+        <v>0.5251022524485742</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9525741268224334</v>
+        <v>0.5748126986354776</v>
       </c>
       <c r="Q3" t="n">
-        <v>25.01778163761718</v>
+        <v>24.99747676581275</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>CONDITIONAL</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.73</v>
+        <v>0.1067</v>
       </c>
       <c r="D4" t="n">
         <v>0.45</v>
       </c>
       <c r="E4" t="n">
-        <v>0.45</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.59</v>
+        <v>0.27835</v>
       </c>
       <c r="G4" t="n">
-        <v>3.681928266954319</v>
+        <v>3.472933266954319</v>
       </c>
       <c r="H4" t="n">
         <v>559.9587933823111</v>
@@ -708,16 +708,16 @@
         <v>0.06008590072953033</v>
       </c>
       <c r="N4" t="n">
-        <v>339830.3838058587</v>
+        <v>15660.31602946806</v>
       </c>
       <c r="O4" t="n">
-        <v>0.003093750000000001</v>
+        <v>0.06820598174426135</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3775406687981454</v>
+        <v>0.01740980682319076</v>
       </c>
       <c r="Q4" t="n">
-        <v>76.96835650541752</v>
+        <v>77.00567284688023</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>CONDITIONAL</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -747,19 +747,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.66</v>
+        <v>0.23241875</v>
       </c>
       <c r="D5" t="n">
         <v>0.65</v>
       </c>
       <c r="E5" t="n">
-        <v>0.65</v>
+        <v>0.0991666666666666</v>
       </c>
       <c r="F5" t="n">
-        <v>0.655</v>
+        <v>0.441209375</v>
       </c>
       <c r="G5" t="n">
-        <v>3.927581261068365</v>
+        <v>3.672152406901698</v>
       </c>
       <c r="H5" t="n">
         <v>445.0016450164403</v>
@@ -780,16 +780,16 @@
         <v>0.05105306819556783</v>
       </c>
       <c r="N5" t="n">
-        <v>1062922.691928466</v>
+        <v>73751.76213019135</v>
       </c>
       <c r="O5" t="n">
-        <v>0.01340625</v>
+        <v>0.2936566222032239</v>
       </c>
       <c r="P5" t="n">
-        <v>0.8175744761936437</v>
+        <v>0.05693915229023641</v>
       </c>
       <c r="Q5" t="n">
-        <v>77.01729817654743</v>
+        <v>76.99884423541256</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -819,19 +819,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.3</v>
+        <v>0.02764166666666665</v>
       </c>
       <c r="D6" t="n">
         <v>0.24</v>
       </c>
       <c r="E6" t="n">
-        <v>0.24</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.27</v>
+        <v>0.1338208333333333</v>
       </c>
       <c r="G6" t="n">
-        <v>3.458479862513614</v>
+        <v>3.342626112513614</v>
       </c>
       <c r="H6" t="n">
         <v>647.1450326913633</v>
@@ -852,16 +852,16 @@
         <v>0.07294071229427213</v>
       </c>
       <c r="N6" t="n">
-        <v>33160.74939210773</v>
+        <v>5073.870036712575</v>
       </c>
       <c r="O6" t="n">
-        <v>0.00066</v>
+        <v>0.03254129502116076</v>
       </c>
       <c r="P6" t="n">
-        <v>0.06913842034334682</v>
+        <v>0.01064631194209305</v>
       </c>
       <c r="Q6" t="n">
-        <v>96.99909455460084</v>
+        <v>97.0066604424583</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
